--- a/input/PL/DoFilesTargets/alignment_targets_disability.xlsx
+++ b/input/PL/DoFilesTargets/alignment_targets_disability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="52" uniqueCount="31">
   <si>
     <t>year</t>
   </si>
@@ -92,6 +92,21 @@
   </si>
   <si>
     <t>29 Mar 2026</t>
+  </si>
+  <si>
+    <t>All persons in the initial population with non-missing healthDsblLongtermFlag</t>
+  </si>
+  <si>
+    <t>healthDsblLongtermFlag == 1 (long-term sick or disabled)</t>
+  </si>
+  <si>
+    <t>Population weights (wgtCrossMainSurvey)</t>
+  </si>
+  <si>
+    <t>SimPaths H2 model only updates healthDsblLongtermFlag for non-retired, non-student persons aged 16+; target denominator includes all ages and statuses</t>
+  </si>
+  <si>
+    <t>28 Apr 2026</t>
   </si>
 </sst>
 </file>
@@ -102,7 +117,111 @@
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="53">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -220,7 +339,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -410,11 +529,193 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -517,6 +818,110 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="26" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="35" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="37" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="40" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="41" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="42" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="43" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="44" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="46" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="48" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="49" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="50" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="51" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="52" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -541,106 +946,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="27">
         <v>2011</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="40">
         <v>0.035999894142150879</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="28">
         <v>2012</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="41">
         <v>0.03489593043923378</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3">
+      <c r="A4" s="29">
         <v>2013</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="42">
         <v>0.032771073281764984</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4">
+      <c r="A5" s="30">
         <v>2014</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="43">
         <v>0.033667176961898804</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="31">
         <v>2015</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="44">
         <v>0.034116044640541077</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6">
+      <c r="A7" s="32">
         <v>2016</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="45">
         <v>0.032127592712640762</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7">
+      <c r="A8" s="33">
         <v>2017</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="46">
         <v>0.029024042189121246</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8">
+      <c r="A9" s="34">
         <v>2018</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="47">
         <v>0.025687271729111671</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="35">
         <v>2019</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="48">
         <v>0.025373056530952454</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10">
+      <c r="A11" s="36">
         <v>2020</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="49">
         <v>0.024366777390241623</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11">
+      <c r="A12" s="37">
         <v>2021</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="50">
         <v>0.028718793764710426</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12">
+      <c r="A13" s="38">
         <v>2022</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="51">
         <v>0.02631850354373455</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13">
+      <c r="A14" s="39">
         <v>2023</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="52">
         <v>0.024158589541912079</v>
       </c>
     </row>
@@ -674,7 +1079,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -682,7 +1087,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -698,7 +1103,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -706,7 +1111,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -746,7 +1151,7 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
